--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,31 @@
           <t>Semana 1 - Cierre</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Semana 2 - Fecha</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Semana 2 - Apertura</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Semana 2 - Máximo</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Semana 2 - Mínimo</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Semana 2 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -471,6 +496,23 @@
       <c r="F2" t="n">
         <v>6089.92</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>6094.85</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6400.08</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5863.46</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6089.92</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -495,6 +537,23 @@
       <c r="F3" t="n">
         <v>62825</v>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>65600</v>
+      </c>
+      <c r="I3" t="n">
+        <v>66600</v>
+      </c>
+      <c r="J3" t="n">
+        <v>61800</v>
+      </c>
+      <c r="K3" t="n">
+        <v>62825</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -519,6 +578,23 @@
       <c r="F4" t="n">
         <v>4702.5</v>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>4967.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4967.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4500</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4702.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -543,6 +619,23 @@
       <c r="F5" t="n">
         <v>10870</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>10870</v>
+      </c>
+      <c r="I5" t="n">
+        <v>11590</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10200</v>
+      </c>
+      <c r="K5" t="n">
+        <v>10870</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -567,6 +660,23 @@
       <c r="F6" t="n">
         <v>667</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>670</v>
+      </c>
+      <c r="I6" t="n">
+        <v>708</v>
+      </c>
+      <c r="J6" t="n">
+        <v>655</v>
+      </c>
+      <c r="K6" t="n">
+        <v>667</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -591,6 +701,23 @@
       <c r="F7" t="n">
         <v>910.5</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>970</v>
+      </c>
+      <c r="I7" t="n">
+        <v>970</v>
+      </c>
+      <c r="J7" t="n">
+        <v>881</v>
+      </c>
+      <c r="K7" t="n">
+        <v>910.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -615,6 +742,23 @@
       <c r="F8" t="n">
         <v>2106</v>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2180</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2299</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2085</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2106</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -639,6 +783,23 @@
       <c r="F9" t="n">
         <v>1754</v>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1869</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1910</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1743</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1754</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -663,6 +824,23 @@
       <c r="F10" t="n">
         <v>3270</v>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>3360</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3590</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3125</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3270</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -685,6 +863,23 @@
         <v>8610</v>
       </c>
       <c r="F11" t="n">
+        <v>8795</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>9095</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9640</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8610</v>
+      </c>
+      <c r="K11" t="n">
         <v>8795</v>
       </c>
     </row>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,31 @@
           <t>Semana 2 - Cierre</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Semana 3 - Fecha</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Semana 3 - Apertura</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Semana 3 - Máximo</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Semana 3 - Mínimo</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Semana 3 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -513,6 +538,23 @@
       <c r="K2" t="n">
         <v>6089.92</v>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>6094.85</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6400.08</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5863.46</v>
+      </c>
+      <c r="P2" t="n">
+        <v>6089.92</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -554,6 +596,23 @@
       <c r="K3" t="n">
         <v>62825</v>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>65600</v>
+      </c>
+      <c r="N3" t="n">
+        <v>66600</v>
+      </c>
+      <c r="O3" t="n">
+        <v>61800</v>
+      </c>
+      <c r="P3" t="n">
+        <v>62825</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -595,6 +654,23 @@
       <c r="K4" t="n">
         <v>4702.5</v>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>4967.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4967.5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4500</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4702.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -636,6 +712,23 @@
       <c r="K5" t="n">
         <v>10870</v>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>10870</v>
+      </c>
+      <c r="N5" t="n">
+        <v>11590</v>
+      </c>
+      <c r="O5" t="n">
+        <v>10200</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10870</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -677,6 +770,23 @@
       <c r="K6" t="n">
         <v>667</v>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>670</v>
+      </c>
+      <c r="N6" t="n">
+        <v>708</v>
+      </c>
+      <c r="O6" t="n">
+        <v>655</v>
+      </c>
+      <c r="P6" t="n">
+        <v>667</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -718,6 +828,23 @@
       <c r="K7" t="n">
         <v>910.5</v>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>970</v>
+      </c>
+      <c r="N7" t="n">
+        <v>970</v>
+      </c>
+      <c r="O7" t="n">
+        <v>881</v>
+      </c>
+      <c r="P7" t="n">
+        <v>910.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -759,6 +886,23 @@
       <c r="K8" t="n">
         <v>2106</v>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>2180</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2299</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2085</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2106</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -800,6 +944,23 @@
       <c r="K9" t="n">
         <v>1754</v>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1869</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1910</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1743</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1754</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -841,6 +1002,23 @@
       <c r="K10" t="n">
         <v>3270</v>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>3360</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3590</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3125</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3270</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -880,6 +1058,23 @@
         <v>8610</v>
       </c>
       <c r="K11" t="n">
+        <v>8795</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>9095</v>
+      </c>
+      <c r="N11" t="n">
+        <v>9640</v>
+      </c>
+      <c r="O11" t="n">
+        <v>8610</v>
+      </c>
+      <c r="P11" t="n">
         <v>8795</v>
       </c>
     </row>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,6 +497,31 @@
           <t>Semana 3 - Cierre</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Semana 4 - Fecha</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Semana 4 - Apertura</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Semana 4 - Máximo</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Semana 4 - Mínimo</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Semana 4 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -555,6 +580,23 @@
       <c r="P2" t="n">
         <v>6089.92</v>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>6094.85</v>
+      </c>
+      <c r="S2" t="n">
+        <v>6400.08</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5863.46</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6089.92</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -613,6 +655,23 @@
       <c r="P3" t="n">
         <v>62825</v>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>65600</v>
+      </c>
+      <c r="S3" t="n">
+        <v>66600</v>
+      </c>
+      <c r="T3" t="n">
+        <v>61800</v>
+      </c>
+      <c r="U3" t="n">
+        <v>62825</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -671,6 +730,23 @@
       <c r="P4" t="n">
         <v>4702.5</v>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>4967.5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4967.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4500</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4702.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -729,6 +805,23 @@
       <c r="P5" t="n">
         <v>10870</v>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>10870</v>
+      </c>
+      <c r="S5" t="n">
+        <v>11590</v>
+      </c>
+      <c r="T5" t="n">
+        <v>10200</v>
+      </c>
+      <c r="U5" t="n">
+        <v>10870</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -787,6 +880,23 @@
       <c r="P6" t="n">
         <v>667</v>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>670</v>
+      </c>
+      <c r="S6" t="n">
+        <v>708</v>
+      </c>
+      <c r="T6" t="n">
+        <v>655</v>
+      </c>
+      <c r="U6" t="n">
+        <v>667</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -845,6 +955,23 @@
       <c r="P7" t="n">
         <v>910.5</v>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>970</v>
+      </c>
+      <c r="S7" t="n">
+        <v>970</v>
+      </c>
+      <c r="T7" t="n">
+        <v>881</v>
+      </c>
+      <c r="U7" t="n">
+        <v>910.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -903,6 +1030,23 @@
       <c r="P8" t="n">
         <v>2106</v>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>2180</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2299</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2085</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2106</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -961,6 +1105,23 @@
       <c r="P9" t="n">
         <v>1754</v>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>1869</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1910</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1743</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1754</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1019,6 +1180,23 @@
       <c r="P10" t="n">
         <v>3270</v>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>3360</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3590</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3125</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3270</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1075,6 +1253,23 @@
         <v>8610</v>
       </c>
       <c r="P11" t="n">
+        <v>8795</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>9095</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9640</v>
+      </c>
+      <c r="T11" t="n">
+        <v>8610</v>
+      </c>
+      <c r="U11" t="n">
         <v>8795</v>
       </c>
     </row>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,81 +447,6 @@
           <t>Semana 1 - Cierre</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Semana 2 - Fecha</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Semana 2 - Apertura</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Semana 2 - Máximo</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Semana 2 - Mínimo</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Semana 2 - Cierre</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Semana 3 - Fecha</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Semana 3 - Apertura</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Semana 3 - Máximo</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Semana 3 - Mínimo</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Semana 3 - Cierre</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Semana 4 - Fecha</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Semana 4 - Apertura</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Semana 4 - Máximo</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Semana 4 - Mínimo</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Semana 4 - Cierre</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -546,57 +471,6 @@
       <c r="F2" t="n">
         <v>6089.92</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>6094.85</v>
-      </c>
-      <c r="I2" t="n">
-        <v>6400.08</v>
-      </c>
-      <c r="J2" t="n">
-        <v>5863.46</v>
-      </c>
-      <c r="K2" t="n">
-        <v>6089.92</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>6094.85</v>
-      </c>
-      <c r="N2" t="n">
-        <v>6400.08</v>
-      </c>
-      <c r="O2" t="n">
-        <v>5863.46</v>
-      </c>
-      <c r="P2" t="n">
-        <v>6089.92</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>6094.85</v>
-      </c>
-      <c r="S2" t="n">
-        <v>6400.08</v>
-      </c>
-      <c r="T2" t="n">
-        <v>5863.46</v>
-      </c>
-      <c r="U2" t="n">
-        <v>6089.92</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -621,57 +495,6 @@
       <c r="F3" t="n">
         <v>62825</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>65600</v>
-      </c>
-      <c r="I3" t="n">
-        <v>66600</v>
-      </c>
-      <c r="J3" t="n">
-        <v>61800</v>
-      </c>
-      <c r="K3" t="n">
-        <v>62825</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>65600</v>
-      </c>
-      <c r="N3" t="n">
-        <v>66600</v>
-      </c>
-      <c r="O3" t="n">
-        <v>61800</v>
-      </c>
-      <c r="P3" t="n">
-        <v>62825</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
-        <v>65600</v>
-      </c>
-      <c r="S3" t="n">
-        <v>66600</v>
-      </c>
-      <c r="T3" t="n">
-        <v>61800</v>
-      </c>
-      <c r="U3" t="n">
-        <v>62825</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -696,57 +519,6 @@
       <c r="F4" t="n">
         <v>4702.5</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>4967.5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>4967.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4500</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4702.5</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>4967.5</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4967.5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>4500</v>
-      </c>
-      <c r="P4" t="n">
-        <v>4702.5</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>4967.5</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4967.5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>4500</v>
-      </c>
-      <c r="U4" t="n">
-        <v>4702.5</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -771,57 +543,6 @@
       <c r="F5" t="n">
         <v>10870</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>10870</v>
-      </c>
-      <c r="I5" t="n">
-        <v>11590</v>
-      </c>
-      <c r="J5" t="n">
-        <v>10200</v>
-      </c>
-      <c r="K5" t="n">
-        <v>10870</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>10870</v>
-      </c>
-      <c r="N5" t="n">
-        <v>11590</v>
-      </c>
-      <c r="O5" t="n">
-        <v>10200</v>
-      </c>
-      <c r="P5" t="n">
-        <v>10870</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>10870</v>
-      </c>
-      <c r="S5" t="n">
-        <v>11590</v>
-      </c>
-      <c r="T5" t="n">
-        <v>10200</v>
-      </c>
-      <c r="U5" t="n">
-        <v>10870</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -846,57 +567,6 @@
       <c r="F6" t="n">
         <v>667</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>670</v>
-      </c>
-      <c r="I6" t="n">
-        <v>708</v>
-      </c>
-      <c r="J6" t="n">
-        <v>655</v>
-      </c>
-      <c r="K6" t="n">
-        <v>667</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>670</v>
-      </c>
-      <c r="N6" t="n">
-        <v>708</v>
-      </c>
-      <c r="O6" t="n">
-        <v>655</v>
-      </c>
-      <c r="P6" t="n">
-        <v>667</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
-        <v>670</v>
-      </c>
-      <c r="S6" t="n">
-        <v>708</v>
-      </c>
-      <c r="T6" t="n">
-        <v>655</v>
-      </c>
-      <c r="U6" t="n">
-        <v>667</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -921,57 +591,6 @@
       <c r="F7" t="n">
         <v>910.5</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>970</v>
-      </c>
-      <c r="I7" t="n">
-        <v>970</v>
-      </c>
-      <c r="J7" t="n">
-        <v>881</v>
-      </c>
-      <c r="K7" t="n">
-        <v>910.5</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>970</v>
-      </c>
-      <c r="N7" t="n">
-        <v>970</v>
-      </c>
-      <c r="O7" t="n">
-        <v>881</v>
-      </c>
-      <c r="P7" t="n">
-        <v>910.5</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="R7" t="n">
-        <v>970</v>
-      </c>
-      <c r="S7" t="n">
-        <v>970</v>
-      </c>
-      <c r="T7" t="n">
-        <v>881</v>
-      </c>
-      <c r="U7" t="n">
-        <v>910.5</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -996,57 +615,6 @@
       <c r="F8" t="n">
         <v>2106</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>2180</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2299</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2085</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2106</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>2180</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2299</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2085</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2106</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
-        <v>2180</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2299</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2085</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2106</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1071,57 +639,6 @@
       <c r="F9" t="n">
         <v>1754</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1869</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1910</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1743</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1754</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>1869</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1910</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1743</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1754</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="R9" t="n">
-        <v>1869</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1910</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1743</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1754</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1146,57 +663,6 @@
       <c r="F10" t="n">
         <v>3270</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>3360</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3590</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3125</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3270</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>3360</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3590</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3125</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3270</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>3360</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3590</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3125</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3270</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1219,57 +685,6 @@
         <v>8610</v>
       </c>
       <c r="F11" t="n">
-        <v>8795</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>9095</v>
-      </c>
-      <c r="I11" t="n">
-        <v>9640</v>
-      </c>
-      <c r="J11" t="n">
-        <v>8610</v>
-      </c>
-      <c r="K11" t="n">
-        <v>8795</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>9095</v>
-      </c>
-      <c r="N11" t="n">
-        <v>9640</v>
-      </c>
-      <c r="O11" t="n">
-        <v>8610</v>
-      </c>
-      <c r="P11" t="n">
-        <v>8795</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="R11" t="n">
-        <v>9095</v>
-      </c>
-      <c r="S11" t="n">
-        <v>9640</v>
-      </c>
-      <c r="T11" t="n">
-        <v>8610</v>
-      </c>
-      <c r="U11" t="n">
         <v>8795</v>
       </c>
     </row>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0090EE90"/>
+        <bgColor rgb="0090EE90"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +454,31 @@
           <t>Semana 1 - Cierre</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Semana 2 - Fecha</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Semana 2 - Apertura</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Semana 2 - Máximo</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Semana 2 - Mínimo</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Semana 2 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -471,6 +503,23 @@
       <c r="F2" t="n">
         <v>6089.92</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>6235</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6450</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6060</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -495,6 +544,23 @@
       <c r="F3" t="n">
         <v>62825</v>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>63225</v>
+      </c>
+      <c r="I3" t="n">
+        <v>67725</v>
+      </c>
+      <c r="J3" t="n">
+        <v>63025</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>65000</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -519,6 +585,23 @@
       <c r="F4" t="n">
         <v>4702.5</v>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>4710</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4895</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4682.5</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>4720</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -543,6 +626,23 @@
       <c r="F5" t="n">
         <v>10870</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>10900</v>
+      </c>
+      <c r="I5" t="n">
+        <v>11230</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10390</v>
+      </c>
+      <c r="K5" t="n">
+        <v>10550</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -567,6 +667,23 @@
       <c r="F6" t="n">
         <v>667</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>667</v>
+      </c>
+      <c r="I6" t="n">
+        <v>670</v>
+      </c>
+      <c r="J6" t="n">
+        <v>593</v>
+      </c>
+      <c r="K6" t="n">
+        <v>615</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -591,6 +708,23 @@
       <c r="F7" t="n">
         <v>910.5</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>911.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>954</v>
+      </c>
+      <c r="J7" t="n">
+        <v>890.5</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>940.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -615,6 +749,23 @@
       <c r="F8" t="n">
         <v>2106</v>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2135</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2199</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2040</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2049</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -639,6 +790,23 @@
       <c r="F9" t="n">
         <v>1754</v>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1843</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1659</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1667</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -663,6 +831,23 @@
       <c r="F10" t="n">
         <v>3270</v>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>3350</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3350</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3050</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3105</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -686,6 +871,23 @@
       </c>
       <c r="F11" t="n">
         <v>8795</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>8795</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9160</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8650</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8750</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -37,6 +37,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="0090EE90"/>
         <bgColor rgb="0090EE90"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFA500"/>
+        <bgColor rgb="00FFA500"/>
       </patternFill>
     </fill>
   </fills>
@@ -52,9 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +486,31 @@
           <t>Semana 2 - Cierre</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Semana 3 - Fecha</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Semana 3 - Apertura</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Semana 3 - Máximo</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Semana 3 - Mínimo</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Semana 3 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -520,6 +552,23 @@
       <c r="K2" t="n">
         <v>6060</v>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>6120</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6600</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5950</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>6455</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -561,6 +610,23 @@
       <c r="K3" s="1" t="n">
         <v>65000</v>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>65400</v>
+      </c>
+      <c r="N3" t="n">
+        <v>72900</v>
+      </c>
+      <c r="O3" t="n">
+        <v>65400</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>71025</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -602,6 +668,23 @@
       <c r="K4" s="1" t="n">
         <v>4720</v>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>4750</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4995</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>4632.5</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>4782.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -643,6 +726,23 @@
       <c r="K5" t="n">
         <v>10550</v>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>10550</v>
+      </c>
+      <c r="N5" t="n">
+        <v>11720</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>10160</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>11280</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -684,6 +784,23 @@
       <c r="K6" t="n">
         <v>615</v>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>615</v>
+      </c>
+      <c r="N6" t="n">
+        <v>643</v>
+      </c>
+      <c r="O6" t="n">
+        <v>601.5</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>634</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -725,6 +842,23 @@
       <c r="K7" s="1" t="n">
         <v>940.5</v>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>940</v>
+      </c>
+      <c r="N7" t="n">
+        <v>949</v>
+      </c>
+      <c r="O7" t="n">
+        <v>894.5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>938.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -766,6 +900,23 @@
       <c r="K8" t="n">
         <v>2049</v>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>2045</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2186</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>2077</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -807,6 +958,23 @@
       <c r="K9" t="n">
         <v>1667</v>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1660</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1873</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>1655</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>1802</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -848,6 +1016,23 @@
       <c r="K10" t="n">
         <v>3105</v>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>3105</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3380</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3060</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>3277.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -888,6 +1073,23 @@
       </c>
       <c r="K11" t="n">
         <v>8750</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>8830</v>
+      </c>
+      <c r="N11" t="n">
+        <v>9300</v>
+      </c>
+      <c r="O11" t="n">
+        <v>8420</v>
+      </c>
+      <c r="P11" t="n">
+        <v>8685</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,6 +511,31 @@
           <t>Semana 3 - Cierre</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Semana 4 - Fecha</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Semana 4 - Apertura</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Semana 4 - Máximo</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Semana 4 - Mínimo</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Semana 4 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -569,6 +594,23 @@
       <c r="P2" s="1" t="n">
         <v>6455</v>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>6455</v>
+      </c>
+      <c r="S2" t="n">
+        <v>7540</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6455</v>
+      </c>
+      <c r="U2" s="1" t="n">
+        <v>7495</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -627,6 +669,23 @@
       <c r="P3" s="1" t="n">
         <v>71025</v>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>71025</v>
+      </c>
+      <c r="S3" t="n">
+        <v>79300</v>
+      </c>
+      <c r="T3" t="n">
+        <v>70300</v>
+      </c>
+      <c r="U3" s="1" t="n">
+        <v>78350</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -685,6 +744,23 @@
       <c r="P4" s="1" t="n">
         <v>4782.5</v>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>4782.5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5110</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4730</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>5080</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -743,6 +819,23 @@
       <c r="P5" s="1" t="n">
         <v>11280</v>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>11280</v>
+      </c>
+      <c r="S5" t="n">
+        <v>13620</v>
+      </c>
+      <c r="T5" t="n">
+        <v>11270</v>
+      </c>
+      <c r="U5" s="1" t="n">
+        <v>13490</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -801,6 +894,23 @@
       <c r="P6" s="1" t="n">
         <v>634</v>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>634</v>
+      </c>
+      <c r="S6" t="n">
+        <v>696</v>
+      </c>
+      <c r="T6" t="n">
+        <v>630</v>
+      </c>
+      <c r="U6" s="1" t="n">
+        <v>692.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -859,6 +969,23 @@
       <c r="P7" t="n">
         <v>938.5</v>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>938.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1021</v>
+      </c>
+      <c r="T7" t="n">
+        <v>920</v>
+      </c>
+      <c r="U7" s="1" t="n">
+        <v>1019</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -917,6 +1044,23 @@
       <c r="P8" s="1" t="n">
         <v>2077</v>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>2077</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2375</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2066</v>
+      </c>
+      <c r="U8" s="1" t="n">
+        <v>2356</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -975,6 +1119,23 @@
       <c r="P9" s="1" t="n">
         <v>1802</v>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>1802</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2110</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1788</v>
+      </c>
+      <c r="U9" s="1" t="n">
+        <v>2062</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1033,6 +1194,23 @@
       <c r="P10" s="1" t="n">
         <v>3277.5</v>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>3277.5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3620</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3277.5</v>
+      </c>
+      <c r="U10" s="1" t="n">
+        <v>3592.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1090,6 +1268,23 @@
       </c>
       <c r="P11" t="n">
         <v>8685</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>8685</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9250</v>
+      </c>
+      <c r="T11" t="n">
+        <v>8500</v>
+      </c>
+      <c r="U11" s="1" t="n">
+        <v>9135</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,6 +536,31 @@
           <t>Semana 4 - Cierre</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Semana 5 - Fecha</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Semana 5 - Apertura</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Semana 5 - Máximo</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Semana 5 - Mínimo</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Semana 5 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -611,6 +636,23 @@
       <c r="U2" s="1" t="n">
         <v>7495</v>
       </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>7490</v>
+      </c>
+      <c r="X2" t="n">
+        <v>7725</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>7135</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>7205</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -686,6 +728,23 @@
       <c r="U3" s="1" t="n">
         <v>78350</v>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>78650</v>
+      </c>
+      <c r="X3" t="n">
+        <v>87225</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>78650</v>
+      </c>
+      <c r="Z3" s="1" t="n">
+        <v>81075</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -761,6 +820,23 @@
       <c r="U4" s="1" t="n">
         <v>5080</v>
       </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>5130</v>
+      </c>
+      <c r="X4" t="n">
+        <v>5310</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4910</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4940</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -836,6 +912,23 @@
       <c r="U5" s="1" t="n">
         <v>13490</v>
       </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>13440</v>
+      </c>
+      <c r="X5" t="n">
+        <v>13840</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>12690</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>12820</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -911,6 +1004,23 @@
       <c r="U6" s="1" t="n">
         <v>692.5</v>
       </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>700</v>
+      </c>
+      <c r="X6" t="n">
+        <v>710</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>668</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>684</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -986,6 +1096,23 @@
       <c r="U7" s="1" t="n">
         <v>1019</v>
       </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>1025</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1035</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>960.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>976</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1061,6 +1188,23 @@
       <c r="U8" s="1" t="n">
         <v>2356</v>
       </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>2352</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2449</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2199</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2226</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1136,6 +1280,23 @@
       <c r="U9" s="1" t="n">
         <v>2062</v>
       </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>2080</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2150</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1940</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1976</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1211,6 +1372,23 @@
       <c r="U10" s="1" t="n">
         <v>3592.5</v>
       </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>3580</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3772.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>3312.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3347.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1285,6 +1463,23 @@
       </c>
       <c r="U11" s="1" t="n">
         <v>9135</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>9205</v>
+      </c>
+      <c r="X11" t="n">
+        <v>9560</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8825</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>8935</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:AE11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,6 +561,31 @@
           <t>Semana 5 - Cierre</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Semana 6 - Fecha</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Semana 6 - Apertura</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Semana 6 - Máximo</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Semana 6 - Mínimo</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Semana 6 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -653,6 +678,23 @@
       <c r="Z2" t="n">
         <v>7205</v>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>7300</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8450</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>7150</v>
+      </c>
+      <c r="AE2" s="1" t="n">
+        <v>8210</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -745,6 +787,23 @@
       <c r="Z3" s="1" t="n">
         <v>81075</v>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>81100</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>85750</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>79500</v>
+      </c>
+      <c r="AE3" s="1" t="n">
+        <v>83400</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -837,6 +896,23 @@
       <c r="Z4" t="n">
         <v>4940</v>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>4950</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5385</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>4950</v>
+      </c>
+      <c r="AE4" s="1" t="n">
+        <v>5290</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -929,6 +1005,23 @@
       <c r="Z5" t="n">
         <v>12820</v>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>12850</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>15100</v>
+      </c>
+      <c r="AD5" s="2" t="n">
+        <v>12650</v>
+      </c>
+      <c r="AE5" s="1" t="n">
+        <v>14810</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1021,6 +1114,23 @@
       <c r="Z6" t="n">
         <v>684</v>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>686.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>706</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>670</v>
+      </c>
+      <c r="AE6" s="1" t="n">
+        <v>699.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1113,6 +1223,23 @@
       <c r="Z7" t="n">
         <v>976</v>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>973</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1034</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>966.5</v>
+      </c>
+      <c r="AE7" s="1" t="n">
+        <v>1029</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1205,6 +1332,23 @@
       <c r="Z8" t="n">
         <v>2226</v>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>2225</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2420</v>
+      </c>
+      <c r="AD8" s="2" t="n">
+        <v>2176</v>
+      </c>
+      <c r="AE8" s="1" t="n">
+        <v>2371</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1297,6 +1441,23 @@
       <c r="Z9" t="n">
         <v>1976</v>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>1951</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2167</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1940</v>
+      </c>
+      <c r="AE9" s="1" t="n">
+        <v>2076</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1389,6 +1550,23 @@
       <c r="Z10" t="n">
         <v>3347.5</v>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>3360</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3825</v>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v>3307.5</v>
+      </c>
+      <c r="AE10" s="1" t="n">
+        <v>3737.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1480,6 +1658,23 @@
       </c>
       <c r="Z11" t="n">
         <v>8935</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>8960</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>10050</v>
+      </c>
+      <c r="AD11" s="2" t="n">
+        <v>8750</v>
+      </c>
+      <c r="AE11" s="1" t="n">
+        <v>9890</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE11"/>
+  <dimension ref="A1:AJ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,6 +586,31 @@
           <t>Semana 6 - Cierre</t>
         </is>
       </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Semana 7 - Fecha</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Semana 7 - Apertura</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Semana 7 - Máximo</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Semana 7 - Mínimo</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Semana 7 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -695,6 +720,23 @@
       <c r="AE2" s="1" t="n">
         <v>8210</v>
       </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>8210</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>8725</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>8105</v>
+      </c>
+      <c r="AJ2" s="1" t="n">
+        <v>8260</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -804,6 +846,23 @@
       <c r="AE3" s="1" t="n">
         <v>83400</v>
       </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>83400</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>83400</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>74950</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>76425</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -913,6 +972,23 @@
       <c r="AE4" s="1" t="n">
         <v>5290</v>
       </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>5290</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>5300</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5085</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>5190</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1022,6 +1098,23 @@
       <c r="AE5" s="1" t="n">
         <v>14810</v>
       </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>14810</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>15610</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>13800</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>14650</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1131,6 +1224,23 @@
       <c r="AE6" s="1" t="n">
         <v>699.5</v>
       </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>699.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>708</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>671</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>674.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1240,6 +1350,23 @@
       <c r="AE7" s="1" t="n">
         <v>1029</v>
       </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1029</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1031</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>965</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1349,6 +1476,23 @@
       <c r="AE8" s="1" t="n">
         <v>2371</v>
       </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>2371</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>2435</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>2300</v>
+      </c>
+      <c r="AJ8" s="1" t="n">
+        <v>2393</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1458,6 +1602,23 @@
       <c r="AE9" s="1" t="n">
         <v>2076</v>
       </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>2076</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2145</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>2036</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2072</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1567,6 +1728,23 @@
       <c r="AE10" s="1" t="n">
         <v>3737.5</v>
       </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>3737.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>3860</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>3420</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>3552.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1675,6 +1853,23 @@
       </c>
       <c r="AE11" s="1" t="n">
         <v>9890</v>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>9890</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>9900</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>9200</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>9730</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ11"/>
+  <dimension ref="A1:AO11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,6 +611,31 @@
           <t>Semana 7 - Cierre</t>
         </is>
       </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Semana 8 - Fecha</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Semana 8 - Apertura</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>Semana 8 - Máximo</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>Semana 8 - Mínimo</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>Semana 8 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -737,6 +762,23 @@
       <c r="AJ2" s="1" t="n">
         <v>8260</v>
       </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AL2" t="n">
+        <v>8395</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>8515</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>7550</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>7715</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -863,6 +905,23 @@
       <c r="AJ3" t="n">
         <v>76425</v>
       </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AL3" t="n">
+        <v>75500</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>77300</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>69000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>70050</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -989,6 +1048,23 @@
       <c r="AJ4" t="n">
         <v>5190</v>
       </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AL4" t="n">
+        <v>5190</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>5300</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>4900</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>4972.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1115,6 +1191,23 @@
       <c r="AJ5" t="n">
         <v>14650</v>
       </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AL5" t="n">
+        <v>14850</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>15300</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>13600</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>14110</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1241,6 +1334,23 @@
       <c r="AJ6" t="n">
         <v>674.5</v>
       </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AL6" t="n">
+        <v>675</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>686.5</v>
+      </c>
+      <c r="AN6" s="2" t="n">
+        <v>646</v>
+      </c>
+      <c r="AO6" s="1" t="n">
+        <v>683.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1367,6 +1477,23 @@
       <c r="AJ7" t="n">
         <v>1000</v>
       </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AL7" t="n">
+        <v>1001</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1045</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>975.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>991</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1493,6 +1620,23 @@
       <c r="AJ8" s="1" t="n">
         <v>2393</v>
       </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AL8" t="n">
+        <v>2407</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>2418</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>2155</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2274</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1619,6 +1763,23 @@
       <c r="AJ9" t="n">
         <v>2072</v>
       </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AL9" t="n">
+        <v>2071</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>2095</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1850</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1891</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1745,6 +1906,23 @@
       <c r="AJ10" t="n">
         <v>3552.5</v>
       </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AL10" t="n">
+        <v>3600</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>3810</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>3480</v>
+      </c>
+      <c r="AO10" s="1" t="n">
+        <v>3555</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1870,6 +2048,23 @@
       </c>
       <c r="AJ11" t="n">
         <v>9730</v>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
+        <v>9600</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>9705</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>9220</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO11"/>
+  <dimension ref="A1:AT11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,6 +636,31 @@
           <t>Semana 8 - Cierre</t>
         </is>
       </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>Semana 9 - Fecha</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>Semana 9 - Apertura</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>Semana 9 - Máximo</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>Semana 9 - Mínimo</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Semana 9 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -779,6 +804,23 @@
       <c r="AO2" t="n">
         <v>7715</v>
       </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7800</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>8065</v>
+      </c>
+      <c r="AS2" s="2" t="n">
+        <v>7510</v>
+      </c>
+      <c r="AT2" s="1" t="n">
+        <v>7970</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -922,6 +964,23 @@
       <c r="AO3" t="n">
         <v>70050</v>
       </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>71050</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>72500</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>69425</v>
+      </c>
+      <c r="AT3" s="1" t="n">
+        <v>71575</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1065,6 +1124,23 @@
       <c r="AO4" t="n">
         <v>4972.5</v>
       </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>5030</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>5220</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4972.5</v>
+      </c>
+      <c r="AT4" s="1" t="n">
+        <v>5135</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1208,6 +1284,23 @@
       <c r="AO5" t="n">
         <v>14110</v>
       </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>14390</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>14880</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>13900</v>
+      </c>
+      <c r="AT5" s="1" t="n">
+        <v>14520</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1351,6 +1444,23 @@
       <c r="AO6" s="1" t="n">
         <v>683.5</v>
       </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>690</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>690</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>654.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>664</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1494,6 +1604,23 @@
       <c r="AO7" t="n">
         <v>991</v>
       </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>990</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1018</v>
+      </c>
+      <c r="AS7" s="2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AT7" s="1" t="n">
+        <v>993</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1637,6 +1764,23 @@
       <c r="AO8" t="n">
         <v>2274</v>
       </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>2280</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2389</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2219</v>
+      </c>
+      <c r="AT8" s="1" t="n">
+        <v>2323</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1780,6 +1924,23 @@
       <c r="AO9" t="n">
         <v>1891</v>
       </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1900</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1896</v>
+      </c>
+      <c r="AT9" s="1" t="n">
+        <v>1956</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1923,6 +2084,23 @@
       <c r="AO10" s="1" t="n">
         <v>3555</v>
       </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>3555</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3750</v>
+      </c>
+      <c r="AS10" s="2" t="n">
+        <v>3465</v>
+      </c>
+      <c r="AT10" s="1" t="n">
+        <v>3672.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2065,6 +2243,23 @@
       </c>
       <c r="AO11" t="n">
         <v>9220</v>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9270</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>9520</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8900</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>9195</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT11"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,6 +661,31 @@
           <t>Semana 9 - Cierre</t>
         </is>
       </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Semana 10 - Fecha</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>Semana 10 - Apertura</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>Semana 10 - Máximo</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>Semana 10 - Mínimo</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>Semana 10 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -821,6 +846,23 @@
       <c r="AT2" s="1" t="n">
         <v>7970</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>8390</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7770</v>
+      </c>
+      <c r="AY2" s="1" t="n">
+        <v>8335</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -981,6 +1023,23 @@
       <c r="AT3" s="1" t="n">
         <v>71575</v>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AV3" t="n">
+        <v>72625</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>78900</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>70500</v>
+      </c>
+      <c r="AY3" s="1" t="n">
+        <v>74400</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1141,6 +1200,23 @@
       <c r="AT4" s="1" t="n">
         <v>5135</v>
       </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AV4" t="n">
+        <v>5130</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>5330</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5080</v>
+      </c>
+      <c r="AY4" s="1" t="n">
+        <v>5180</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1301,6 +1377,23 @@
       <c r="AT5" s="1" t="n">
         <v>14520</v>
       </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AV5" t="n">
+        <v>14540</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>15130</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>14040</v>
+      </c>
+      <c r="AY5" s="1" t="n">
+        <v>14800</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1461,6 +1554,23 @@
       <c r="AT6" t="n">
         <v>664</v>
       </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>665</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>693</v>
+      </c>
+      <c r="AX6" s="2" t="n">
+        <v>641</v>
+      </c>
+      <c r="AY6" s="1" t="n">
+        <v>671</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1621,6 +1731,23 @@
       <c r="AT7" s="1" t="n">
         <v>993</v>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AV7" t="n">
+        <v>993</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1010</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>956</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>975.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1781,6 +1908,23 @@
       <c r="AT8" s="1" t="n">
         <v>2323</v>
       </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AV8" t="n">
+        <v>2310</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2405</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>2263</v>
+      </c>
+      <c r="AY8" s="1" t="n">
+        <v>2396</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1941,6 +2085,23 @@
       <c r="AT9" s="1" t="n">
         <v>1956</v>
       </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AV9" t="n">
+        <v>1960</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2029</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1910</v>
+      </c>
+      <c r="AY9" s="1" t="n">
+        <v>1986</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2101,6 +2262,23 @@
       <c r="AT10" s="1" t="n">
         <v>3672.5</v>
       </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AV10" t="n">
+        <v>3670</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>3797.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3467.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3582.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2260,6 +2438,23 @@
       </c>
       <c r="AT11" t="n">
         <v>9195</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AV11" t="n">
+        <v>9180</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>9610</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>9045</v>
+      </c>
+      <c r="AY11" s="1" t="n">
+        <v>9595</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:BD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,6 +686,31 @@
           <t>Semana 10 - Cierre</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Semana 11 - Fecha</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>Semana 11 - Apertura</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>Semana 11 - Máximo</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>Semana 11 - Mínimo</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>Semana 11 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -863,6 +888,23 @@
       <c r="AY2" s="1" t="n">
         <v>8335</v>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>8385</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>8385</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>7630</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>7860</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1040,6 +1082,23 @@
       <c r="AY3" s="1" t="n">
         <v>74400</v>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="BA3" t="n">
+        <v>75500</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>79375</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>75075</v>
+      </c>
+      <c r="BD3" s="1" t="n">
+        <v>77900</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1217,6 +1276,23 @@
       <c r="AY4" s="1" t="n">
         <v>5180</v>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="BA4" t="n">
+        <v>5105</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5310</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5050</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5170</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1394,6 +1470,23 @@
       <c r="AY5" s="1" t="n">
         <v>14800</v>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
+        <v>14770</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>13730</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>14190</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1571,6 +1664,23 @@
       <c r="AY6" s="1" t="n">
         <v>671</v>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>662</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>675</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>650.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>664</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1748,6 +1858,23 @@
       <c r="AY7" t="n">
         <v>975.5</v>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>980</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>987</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>930</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>949.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1925,6 +2052,23 @@
       <c r="AY8" s="1" t="n">
         <v>2396</v>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="BA8" t="n">
+        <v>2368</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>2415</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2221</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2264</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2102,6 +2246,23 @@
       <c r="AY9" s="1" t="n">
         <v>1986</v>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="BA9" t="n">
+        <v>1986</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>2029</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1910</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1944</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2279,6 +2440,23 @@
       <c r="AY10" t="n">
         <v>3582.5</v>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="BA10" t="n">
+        <v>3565</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>3650</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3465</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>3522.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2455,6 +2633,23 @@
       </c>
       <c r="AY11" s="1" t="n">
         <v>9595</v>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="BA11" t="n">
+        <v>9570</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>9935</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>9205</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>9370</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD11"/>
+  <dimension ref="A1:BI11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -711,6 +711,31 @@
           <t>Semana 11 - Cierre</t>
         </is>
       </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>Semana 12 - Fecha</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>Semana 12 - Apertura</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>Semana 12 - Máximo</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>Semana 12 - Mínimo</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>Semana 12 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -905,6 +930,23 @@
       <c r="BD2" t="n">
         <v>7860</v>
       </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="BF2" t="n">
+        <v>7870</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>8315</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>7720</v>
+      </c>
+      <c r="BI2" s="1" t="n">
+        <v>7890</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1099,6 +1141,23 @@
       <c r="BD3" s="1" t="n">
         <v>77900</v>
       </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="BF3" t="n">
+        <v>78000</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>84400</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>76700</v>
+      </c>
+      <c r="BI3" s="1" t="n">
+        <v>82000</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1293,6 +1352,23 @@
       <c r="BD4" t="n">
         <v>5170</v>
       </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="BF4" t="n">
+        <v>5175</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>5700</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>5115</v>
+      </c>
+      <c r="BI4" s="1" t="n">
+        <v>5515</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1487,6 +1563,23 @@
       <c r="BD5" t="n">
         <v>14190</v>
       </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="BF5" t="n">
+        <v>14210</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>15600</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>13820</v>
+      </c>
+      <c r="BI5" s="1" t="n">
+        <v>14310</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1681,6 +1774,23 @@
       <c r="BD6" t="n">
         <v>664</v>
       </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="BF6" t="n">
+        <v>664</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>688</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>655</v>
+      </c>
+      <c r="BI6" s="1" t="n">
+        <v>674</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1875,6 +1985,23 @@
       <c r="BD7" t="n">
         <v>949.5</v>
       </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="BF7" t="n">
+        <v>953</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>986.5</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>945.5</v>
+      </c>
+      <c r="BI7" s="1" t="n">
+        <v>972</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2069,6 +2196,23 @@
       <c r="BD8" t="n">
         <v>2264</v>
       </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="BF8" t="n">
+        <v>2258</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2445</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>2227</v>
+      </c>
+      <c r="BI8" s="1" t="n">
+        <v>2365</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2263,6 +2407,23 @@
       <c r="BD9" t="n">
         <v>1944</v>
       </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="BF9" t="n">
+        <v>1944</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2150</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1926</v>
+      </c>
+      <c r="BI9" s="1" t="n">
+        <v>2071</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2457,6 +2618,23 @@
       <c r="BD10" t="n">
         <v>3522.5</v>
       </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>3550</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3890</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3480</v>
+      </c>
+      <c r="BI10" s="1" t="n">
+        <v>3610</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2650,6 +2828,23 @@
       </c>
       <c r="BD11" t="n">
         <v>9370</v>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="BF11" t="n">
+        <v>9370</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>10130</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>9240</v>
+      </c>
+      <c r="BI11" s="1" t="n">
+        <v>9765</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI11"/>
+  <dimension ref="A1:BN11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -736,6 +736,31 @@
           <t>Semana 12 - Cierre</t>
         </is>
       </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>Semana 13 - Fecha</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>Semana 13 - Apertura</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>Semana 13 - Máximo</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>Semana 13 - Mínimo</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>Semana 13 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -947,6 +972,23 @@
       <c r="BI2" s="1" t="n">
         <v>7890</v>
       </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="BK2" t="n">
+        <v>7930</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>8195</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>7680</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>7890</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1158,6 +1200,23 @@
       <c r="BI3" s="1" t="n">
         <v>82000</v>
       </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="BK3" t="n">
+        <v>79875</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>83850</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>78700</v>
+      </c>
+      <c r="BN3" s="1" t="n">
+        <v>82900</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1369,6 +1428,23 @@
       <c r="BI4" s="1" t="n">
         <v>5515</v>
       </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="BK4" t="n">
+        <v>5510</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>5650</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>5205</v>
+      </c>
+      <c r="BN4" s="1" t="n">
+        <v>5555</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1580,6 +1656,23 @@
       <c r="BI5" s="1" t="n">
         <v>14310</v>
       </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="BK5" t="n">
+        <v>14500</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>14200</v>
+      </c>
+      <c r="BN5" s="1" t="n">
+        <v>14470</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1791,6 +1884,23 @@
       <c r="BI6" s="1" t="n">
         <v>674</v>
       </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="BK6" t="n">
+        <v>675</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>685.5</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>644</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>659.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2002,6 +2112,23 @@
       <c r="BI7" s="1" t="n">
         <v>972</v>
       </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="BK7" t="n">
+        <v>977</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>998</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>960</v>
+      </c>
+      <c r="BN7" s="1" t="n">
+        <v>977.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2213,6 +2340,23 @@
       <c r="BI8" s="1" t="n">
         <v>2365</v>
       </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="BK8" t="n">
+        <v>2371</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>2491</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>2270</v>
+      </c>
+      <c r="BN8" s="1" t="n">
+        <v>2396</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2424,6 +2568,23 @@
       <c r="BI9" s="1" t="n">
         <v>2071</v>
       </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="BK9" t="n">
+        <v>2076</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>2150</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1970</v>
+      </c>
+      <c r="BN9" s="1" t="n">
+        <v>2121</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2635,6 +2796,23 @@
       <c r="BI10" s="1" t="n">
         <v>3610</v>
       </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="BK10" t="n">
+        <v>3600</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>3760</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>3590</v>
+      </c>
+      <c r="BN10" s="1" t="n">
+        <v>3620</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2845,6 +3023,23 @@
       </c>
       <c r="BI11" s="1" t="n">
         <v>9765</v>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="BK11" t="n">
+        <v>9620</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>10140</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>9350</v>
+      </c>
+      <c r="BN11" s="1" t="n">
+        <v>10050</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN11"/>
+  <dimension ref="A1:BS11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -761,6 +761,31 @@
           <t>Semana 13 - Cierre</t>
         </is>
       </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>Semana 14 - Fecha</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>Semana 14 - Apertura</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>Semana 14 - Máximo</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>Semana 14 - Mínimo</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>Semana 14 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -989,6 +1014,23 @@
       <c r="BN2" t="n">
         <v>7890</v>
       </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="BP2" t="n">
+        <v>7890</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>8055</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>7215</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>7315</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1217,6 +1259,23 @@
       <c r="BN3" s="1" t="n">
         <v>82900</v>
       </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="BP3" t="n">
+        <v>8150</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>8270</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>7635</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>7775</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1445,6 +1504,23 @@
       <c r="BN4" s="1" t="n">
         <v>5555</v>
       </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="BP4" t="n">
+        <v>5555</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>5555</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>5150</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>5205</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1673,6 +1749,23 @@
       <c r="BN5" s="1" t="n">
         <v>14470</v>
       </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="BP5" t="n">
+        <v>14450</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>15030</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>13020</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>13270</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1901,6 +1994,23 @@
       <c r="BN6" t="n">
         <v>659.5</v>
       </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="BP6" t="n">
+        <v>660</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>723</v>
+      </c>
+      <c r="BR6" s="2" t="n">
+        <v>638.5</v>
+      </c>
+      <c r="BS6" s="1" t="n">
+        <v>715.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2129,6 +2239,23 @@
       <c r="BN7" s="1" t="n">
         <v>977.5</v>
       </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="BP7" t="n">
+        <v>983</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>983</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>922</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>934.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2357,6 +2484,23 @@
       <c r="BN8" s="1" t="n">
         <v>2396</v>
       </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="BP8" t="n">
+        <v>2390</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>2395</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>2169</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>2208</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2585,6 +2729,23 @@
       <c r="BN9" s="1" t="n">
         <v>2121</v>
       </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="BP9" t="n">
+        <v>2129</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>2160</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1907</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1923</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2813,6 +2974,23 @@
       <c r="BN10" s="1" t="n">
         <v>3620</v>
       </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="BP10" t="n">
+        <v>3635</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>3660</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>3215</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>3265</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3040,6 +3218,23 @@
       </c>
       <c r="BN11" s="1" t="n">
         <v>10050</v>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="BP11" t="n">
+        <v>10040</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>10080</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>9045</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>9135</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS11"/>
+  <dimension ref="A1:BX11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,31 @@
           <t>Semana 14 - Cierre</t>
         </is>
       </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>Semana 15 - Fecha</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>Semana 15 - Apertura</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>Semana 15 - Máximo</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>Semana 15 - Mínimo</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>Semana 15 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1031,6 +1056,23 @@
       <c r="BS2" t="n">
         <v>7315</v>
       </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="BU2" t="n">
+        <v>7320</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>7520</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>6835</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>6850</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1276,6 +1318,23 @@
       <c r="BS3" t="n">
         <v>7775</v>
       </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="BU3" t="n">
+        <v>7900</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>8370</v>
+      </c>
+      <c r="BW3" s="2" t="n">
+        <v>7600</v>
+      </c>
+      <c r="BX3" s="1" t="n">
+        <v>7860</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1521,6 +1580,23 @@
       <c r="BS4" t="n">
         <v>5205</v>
       </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="BU4" t="n">
+        <v>5215</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>5350</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>4927.5</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>4990</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1766,6 +1842,23 @@
       <c r="BS5" t="n">
         <v>13270</v>
       </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="BU5" t="n">
+        <v>13370</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>13810</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>12200</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>12240</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2011,6 +2104,23 @@
       <c r="BS6" s="1" t="n">
         <v>715.5</v>
       </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="BU6" t="n">
+        <v>716</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>779</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>712</v>
+      </c>
+      <c r="BX6" s="1" t="n">
+        <v>728</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2256,6 +2366,23 @@
       <c r="BS7" t="n">
         <v>934.5</v>
       </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="BU7" t="n">
+        <v>955</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>955.5</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>890</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>898</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2501,6 +2628,23 @@
       <c r="BS8" t="n">
         <v>2208</v>
       </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="BU8" t="n">
+        <v>2205</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>2227</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>2043</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>2072</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2746,6 +2890,23 @@
       <c r="BS9" t="n">
         <v>1923</v>
       </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="BU9" t="n">
+        <v>1929</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1984</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1799</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1829</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2991,6 +3152,23 @@
       <c r="BS10" t="n">
         <v>3265</v>
       </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="BU10" t="n">
+        <v>3300</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>3320</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>2907.5</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>2957.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3235,6 +3413,23 @@
       </c>
       <c r="BS11" t="n">
         <v>9135</v>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="BU11" t="n">
+        <v>9420</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>9445</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>8720</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>8870</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX11"/>
+  <dimension ref="A1:CC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,6 +811,31 @@
           <t>Semana 15 - Cierre</t>
         </is>
       </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>Semana 16 - Fecha</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>Semana 16 - Apertura</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>Semana 16 - Máximo</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>Semana 16 - Mínimo</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>Semana 16 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1073,6 +1098,23 @@
       <c r="BX2" t="n">
         <v>6850</v>
       </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="BZ2" t="n">
+        <v>6850</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>6960</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>6450</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>6620</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1335,6 +1377,23 @@
       <c r="BX3" s="1" t="n">
         <v>7860</v>
       </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="BZ3" t="n">
+        <v>7860</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>8375</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>7860</v>
+      </c>
+      <c r="CC3" s="1" t="n">
+        <v>8150</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1597,6 +1656,23 @@
       <c r="BX4" t="n">
         <v>4990</v>
       </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="BZ4" t="n">
+        <v>4990</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>5160</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>4932.5</v>
+      </c>
+      <c r="CC4" s="1" t="n">
+        <v>5055</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1859,6 +1935,23 @@
       <c r="BX5" t="n">
         <v>12240</v>
       </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="BZ5" t="n">
+        <v>12240</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>12390</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>11300</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>11650</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2121,6 +2214,23 @@
       <c r="BX6" s="1" t="n">
         <v>728</v>
       </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="BZ6" t="n">
+        <v>728</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>735</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>667</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>697</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2383,6 +2493,23 @@
       <c r="BX7" t="n">
         <v>898</v>
       </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="BZ7" t="n">
+        <v>898</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>925</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>845.5</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>870.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2645,6 +2772,23 @@
       <c r="BX8" t="n">
         <v>2072</v>
       </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="BZ8" t="n">
+        <v>2072</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>2102</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>2071</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2907,6 +3051,23 @@
       <c r="BX9" t="n">
         <v>1829</v>
       </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1829</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1844</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>1740</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>1775</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3169,6 +3330,23 @@
       <c r="BX10" t="n">
         <v>2957.5</v>
       </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="BZ10" t="n">
+        <v>2957.5</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>3017.5</v>
+      </c>
+      <c r="CB10" s="2" t="n">
+        <v>2867.5</v>
+      </c>
+      <c r="CC10" s="1" t="n">
+        <v>2965</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3430,6 +3608,23 @@
       </c>
       <c r="BX11" t="n">
         <v>8870</v>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="BZ11" t="n">
+        <v>8870</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>9085</v>
+      </c>
+      <c r="CB11" s="2" t="n">
+        <v>8655</v>
+      </c>
+      <c r="CC11" s="1" t="n">
+        <v>8935</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC11"/>
+  <dimension ref="A1:CH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -836,6 +836,31 @@
           <t>Semana 16 - Cierre</t>
         </is>
       </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>Semana 17 - Fecha</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>Semana 17 - Apertura</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>Semana 17 - Máximo</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>Semana 17 - Mínimo</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>Semana 17 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1115,6 +1140,23 @@
       <c r="CC2" t="n">
         <v>6620</v>
       </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="CE2" t="n">
+        <v>6620</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>7230</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>6560</v>
+      </c>
+      <c r="CH2" s="1" t="n">
+        <v>6810</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1394,6 +1436,23 @@
       <c r="CC3" s="1" t="n">
         <v>8150</v>
       </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="CE3" t="n">
+        <v>8145</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>8290</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>7905</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>8070</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1673,6 +1732,23 @@
       <c r="CC4" s="1" t="n">
         <v>5055</v>
       </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="CE4" t="n">
+        <v>5080</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>5265</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="CH4" s="1" t="n">
+        <v>5175</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1952,6 +2028,23 @@
       <c r="CC5" t="n">
         <v>11650</v>
       </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="CE5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>12790</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>11560</v>
+      </c>
+      <c r="CH5" s="1" t="n">
+        <v>12260</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2231,6 +2324,23 @@
       <c r="CC6" t="n">
         <v>697</v>
       </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="CE6" t="n">
+        <v>704</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>709</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>677</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>687.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2510,6 +2620,23 @@
       <c r="CC7" t="n">
         <v>870.5</v>
       </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="CE7" t="n">
+        <v>874.5</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>888</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>832</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>835.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2789,6 +2916,23 @@
       <c r="CC8" t="n">
         <v>2071</v>
       </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="CE8" t="n">
+        <v>2077</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>2225</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>2031</v>
+      </c>
+      <c r="CH8" s="1" t="n">
+        <v>2141</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3068,6 +3212,23 @@
       <c r="CC9" t="n">
         <v>1775</v>
       </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="CE9" t="n">
+        <v>1780</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>1925</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>1759</v>
+      </c>
+      <c r="CH9" s="1" t="n">
+        <v>1866</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3347,6 +3508,23 @@
       <c r="CC10" s="1" t="n">
         <v>2965</v>
       </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="CE10" t="n">
+        <v>2965</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>3177.5</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>2910</v>
+      </c>
+      <c r="CH10" s="1" t="n">
+        <v>3140</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3625,6 +3803,23 @@
       </c>
       <c r="CC11" s="1" t="n">
         <v>8935</v>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="CE11" t="n">
+        <v>8980</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>9200</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>8815</v>
+      </c>
+      <c r="CH11" s="1" t="n">
+        <v>9010</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH11"/>
+  <dimension ref="A1:CM11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -861,6 +861,31 @@
           <t>Semana 17 - Cierre</t>
         </is>
       </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>Semana 18 - Fecha</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>Semana 18 - Apertura</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>Semana 18 - Máximo</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>Semana 18 - Mínimo</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>Semana 18 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1157,6 +1182,23 @@
       <c r="CH2" s="1" t="n">
         <v>6810</v>
       </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="CJ2" t="n">
+        <v>6800</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>7320</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>6800</v>
+      </c>
+      <c r="CM2" s="1" t="n">
+        <v>7005</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1453,6 +1495,23 @@
       <c r="CH3" t="n">
         <v>8070</v>
       </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="CJ3" t="n">
+        <v>8090</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>8745</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>8090</v>
+      </c>
+      <c r="CM3" s="1" t="n">
+        <v>8355</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1749,6 +1808,23 @@
       <c r="CH4" s="1" t="n">
         <v>5175</v>
       </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="CJ4" t="n">
+        <v>5200</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>5595</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>5175</v>
+      </c>
+      <c r="CM4" s="1" t="n">
+        <v>5365</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2045,6 +2121,23 @@
       <c r="CH5" s="1" t="n">
         <v>12260</v>
       </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="CJ5" t="n">
+        <v>12300</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>12900</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>12170</v>
+      </c>
+      <c r="CM5" s="1" t="n">
+        <v>12480</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2341,6 +2434,23 @@
       <c r="CH6" t="n">
         <v>687.5</v>
       </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="CJ6" t="n">
+        <v>683</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>698</v>
+      </c>
+      <c r="CL6" s="2" t="n">
+        <v>657.5</v>
+      </c>
+      <c r="CM6" s="1" t="n">
+        <v>690.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2637,6 +2747,23 @@
       <c r="CH7" t="n">
         <v>835.5</v>
       </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="CJ7" t="n">
+        <v>854</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>864</v>
+      </c>
+      <c r="CL7" s="2" t="n">
+        <v>814</v>
+      </c>
+      <c r="CM7" s="1" t="n">
+        <v>845</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2933,6 +3060,23 @@
       <c r="CH8" s="1" t="n">
         <v>2141</v>
       </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="CJ8" t="n">
+        <v>2140</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>2315</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>2126</v>
+      </c>
+      <c r="CM8" s="1" t="n">
+        <v>2220</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3229,6 +3373,23 @@
       <c r="CH9" s="1" t="n">
         <v>1866</v>
       </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="CJ9" t="n">
+        <v>1865</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>2015</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>1820</v>
+      </c>
+      <c r="CM9" s="1" t="n">
+        <v>1938</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3525,6 +3686,23 @@
       <c r="CH10" s="1" t="n">
         <v>3140</v>
       </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="CJ10" t="n">
+        <v>3112.5</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>3382.5</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>3112.5</v>
+      </c>
+      <c r="CM10" s="1" t="n">
+        <v>3255</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3820,6 +3998,23 @@
       </c>
       <c r="CH11" s="1" t="n">
         <v>9010</v>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="CJ11" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>9595</v>
+      </c>
+      <c r="CL11" s="2" t="n">
+        <v>8800</v>
+      </c>
+      <c r="CM11" s="1" t="n">
+        <v>9160</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM11"/>
+  <dimension ref="A1:CR11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -886,6 +886,31 @@
           <t>Semana 18 - Cierre</t>
         </is>
       </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>Semana 19 - Fecha</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>Semana 19 - Apertura</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>Semana 19 - Máximo</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>Semana 19 - Mínimo</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>Semana 19 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1199,6 +1224,23 @@
       <c r="CM2" s="1" t="n">
         <v>7005</v>
       </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="CO2" t="n">
+        <v>7040</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>7265</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>6870</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>7000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1512,6 +1554,23 @@
       <c r="CM3" s="1" t="n">
         <v>8355</v>
       </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="CO3" t="n">
+        <v>8450</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>9100</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>8285</v>
+      </c>
+      <c r="CR3" s="1" t="n">
+        <v>8835</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1825,6 +1884,23 @@
       <c r="CM4" s="1" t="n">
         <v>5365</v>
       </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="CO4" t="n">
+        <v>5400</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>5665</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>5290</v>
+      </c>
+      <c r="CR4" s="1" t="n">
+        <v>5525</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2138,6 +2214,23 @@
       <c r="CM5" s="1" t="n">
         <v>12480</v>
       </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="CO5" t="n">
+        <v>12180</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>12890</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>12180</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>12420</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2451,6 +2544,23 @@
       <c r="CM6" s="1" t="n">
         <v>690.5</v>
       </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="CO6" t="n">
+        <v>691</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>705</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>659</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>668</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2764,6 +2874,23 @@
       <c r="CM7" s="1" t="n">
         <v>845</v>
       </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="CO7" t="n">
+        <v>850</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>896</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>815</v>
+      </c>
+      <c r="CR7" s="1" t="n">
+        <v>871.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3077,6 +3204,23 @@
       <c r="CM8" s="1" t="n">
         <v>2220</v>
       </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="CO8" t="n">
+        <v>2225</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>2325</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>2195</v>
+      </c>
+      <c r="CR8" s="1" t="n">
+        <v>2253</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3390,6 +3534,23 @@
       <c r="CM9" s="1" t="n">
         <v>1938</v>
       </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="CO9" t="n">
+        <v>1914</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>2020</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>1902</v>
+      </c>
+      <c r="CR9" s="1" t="n">
+        <v>1954</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3703,6 +3864,23 @@
       <c r="CM10" s="1" t="n">
         <v>3255</v>
       </c>
+      <c r="CN10" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="CO10" t="n">
+        <v>3255</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>3352.5</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>3070</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>3120</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4015,6 +4193,23 @@
       </c>
       <c r="CM11" s="1" t="n">
         <v>9160</v>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="CO11" t="n">
+        <v>9265</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>9880</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>9225</v>
+      </c>
+      <c r="CR11" s="1" t="n">
+        <v>9515</v>
       </c>
     </row>
   </sheetData>
